--- a/04_DESIGN_TABLES/DesignTable_5000_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5000_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,17 +960,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5000-06-04</t>
+          <t>5000-06-02</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.13</v>
       </c>
       <c r="C6" t="n">
-        <v>0.50807</v>
+        <v>0.50518</v>
       </c>
       <c r="D6" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="E6" t="n">
         <v>0.57</v>
@@ -994,37 +994,37 @@
         <v>0.3294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="N6" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0556</v>
+        <v>0.037</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.215</v>
+        <v>0.165</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2594</v>
+        <v>0.1946</v>
       </c>
       <c r="S6" t="n">
         <v>1.13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>5000-06-04</t>
+          <t>5000-06-02</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 3/8-18 NPTF (female) x 1/4-18 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 3/8-18 NPTF (female) x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1049,19 +1049,24 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Air-Way s82 only (double-pass 19 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p10 table TFA-p010-t04 "5000 FP-FP STRAIGHT" row 5000-06-02 col "L LGTH" = "1.130" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 430.3, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p10 5000 drawing: L = overall, C HEX = body hex (impact/F2a.json, certain); same-table check on today's base: 19/19 rows with an Air-Way/OMi value agree with this catalog column to rounding; CHEX@HEX: Brennan TFA catalog p10 table TFA-p010-t04 "5000 FP-FP STRAIGHT" row 5000-06-02 col "C HEX" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 430.3, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p10 5000 drawing: L = overall, C HEX = body hex (impact/F2a.json, certain); same-table check on today's base: 19/19 rows with an Air-Way/OMi value agree with this catalog column to rounding; TAPDRILL1@BORE: end library gen_straight2 FPT[6] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.57, FPT_P1 0.68 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 3/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[6] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; TAPDRILL2@BORE: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[2] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; $PRP@Threads: thread texts from the part-number dashes (NPTF lib), format of the built 5000 rows | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex from the Brennan TFA catalog p10 alone; tap drills = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>5000-06-04</t>
+          <t>5000-06-02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5000-06-06</t>
+          <t>5000-06-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1095,13 +1100,13 @@
         <v>0.3294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="N7" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="O7" t="n">
         <v>0.5649999999999999</v>
@@ -1110,22 +1115,22 @@
         <v>0.0556</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.285</v>
+        <v>0.215</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3294</v>
+        <v>0.2594</v>
       </c>
       <c r="S7" t="n">
         <v>1.13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>5000-06-06</t>
+          <t>5000-06-04</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 3/8-18 NPTF (female) x 3/8-18 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 3/8-18 NPTF (female) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,7 +1145,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1155,78 +1160,78 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>5000-06-06</t>
+          <t>5000-06-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5000-08-04</t>
+          <t>5000-06-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65241</v>
+        <v>0.50807</v>
       </c>
       <c r="D8" t="n">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="L8" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>0.755</v>
+        <v>0.68</v>
       </c>
       <c r="N8" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="O8" t="n">
-        <v>0.67</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="P8" t="n">
         <v>0.0556</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.215</v>
+        <v>0.285</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2594</v>
+        <v>0.3294</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5000-08-04</t>
+          <t>5000-06-06</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 1/2-14 NPTF (female) x 1/4-18 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 3/8-18 NPTF (female) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1236,12 +1241,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1256,14 +1261,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>5000-08-04</t>
+          <t>5000-06-06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5000-08-06</t>
+          <t>5000-08-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1297,37 +1302,37 @@
         <v>0.4071</v>
       </c>
       <c r="L9" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="M9" t="n">
         <v>0.755</v>
       </c>
       <c r="N9" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="O9" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="P9" t="n">
         <v>0.0556</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.285</v>
+        <v>0.215</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3294</v>
+        <v>0.2594</v>
       </c>
       <c r="S9" t="n">
         <v>1.5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5000-08-06</t>
+          <t>5000-08-04</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 1/2-14 NPTF (female) x 3/8-18 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 1/2-14 NPTF (female) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1342,7 +1347,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1357,78 +1362,78 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>5000-08-06</t>
+          <t>5000-08-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5000-12-04</t>
+          <t>5000-08-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D10" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.765</v>
+        <v>0.75</v>
       </c>
       <c r="I10" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="L10" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="M10" t="n">
-        <v>0.77</v>
+        <v>0.755</v>
       </c>
       <c r="N10" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="O10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="P10" t="n">
         <v>0.0556</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.215</v>
+        <v>0.285</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2594</v>
+        <v>0.3294</v>
       </c>
       <c r="S10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>5000-12-04</t>
+          <t>5000-08-06</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 3/4-14 NPTF (female) x 1/4-18 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 1/2-14 NPTF (female) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,12 +1443,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1458,14 +1463,14 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>5000-12-04</t>
+          <t>5000-08-06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5000-12-06</t>
+          <t>5000-12-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1499,37 +1504,37 @@
         <v>0.5121</v>
       </c>
       <c r="L11" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
         <v>0.77</v>
       </c>
       <c r="N11" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="O11" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="P11" t="n">
         <v>0.0556</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.285</v>
+        <v>0.215</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3294</v>
+        <v>0.2594</v>
       </c>
       <c r="S11" t="n">
         <v>1.53</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>5000-12-06</t>
+          <t>5000-12-04</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 3/4-14 NPTF (female) x 3/8-18 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 3/4-14 NPTF (female) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1559,14 +1564,14 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>5000-12-06</t>
+          <t>5000-12-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5000-12-08</t>
+          <t>5000-12-06</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1600,37 +1605,37 @@
         <v>0.5121</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="O12" t="n">
-        <v>0.765</v>
+        <v>0.68</v>
       </c>
       <c r="P12" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="S12" t="n">
         <v>1.53</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>5000-12-08</t>
+          <t>5000-12-06</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 3/4-14 NPTF (female) x 1/2-14 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 3/4-14 NPTF (female) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1645,7 +1650,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1660,14 +1665,14 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>5000-12-08</t>
+          <t>5000-12-06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5000-12-12</t>
+          <t>5000-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1701,13 +1706,13 @@
         <v>0.5121</v>
       </c>
       <c r="L13" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="O13" t="n">
         <v>0.765</v>
@@ -1716,22 +1721,22 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="S13" t="n">
         <v>1.53</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5000-12-12</t>
+          <t>5000-12-08</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 3/4-14 NPTF (female) x 3/4-14 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 3/4-14 NPTF (female) x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1746,7 +1751,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1761,57 +1766,57 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>5000-12-12</t>
+          <t>5000-12-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5000-16-12</t>
+          <t>5000-12-12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="C14" t="n">
-        <v>0.94108</v>
+        <v>0.79674</v>
       </c>
       <c r="D14" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="E14" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="F14" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="G14" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="H14" t="n">
-        <v>0.945</v>
+        <v>0.765</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5121</v>
       </c>
       <c r="L14" t="n">
         <v>0.91</v>
       </c>
       <c r="M14" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="N14" t="n">
         <v>0.91</v>
       </c>
       <c r="O14" t="n">
-        <v>0.91</v>
+        <v>0.765</v>
       </c>
       <c r="P14" t="n">
         <v>0.07140000000000001</v>
@@ -1823,16 +1828,16 @@
         <v>0.5121</v>
       </c>
       <c r="S14" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>5000-16-12</t>
+          <t>5000-12-12</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 1-11 1/2 NPTF (female) x 3/4-14 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 3/4-14 NPTF (female) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1842,7 +1847,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -1862,24 +1867,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>5000-16-12</t>
+          <t>5000-12-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5000-16-16</t>
+          <t>5000-16-08</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1.89</v>
       </c>
       <c r="C15" t="n">
-        <v>0.94108</v>
+        <v>0.93819</v>
       </c>
       <c r="D15" t="n">
-        <v>1.63</v>
+        <v>1.625</v>
       </c>
       <c r="E15" t="n">
         <v>1.14</v>
@@ -1903,37 +1908,37 @@
         <v>0.6395999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="M15" t="n">
-        <v>1.14</v>
+        <v>0.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0.945</v>
+        <v>0.9</v>
       </c>
       <c r="P15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="S15" t="n">
         <v>1.89</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5000-16-16</t>
+          <t>5000-16-08</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 1-11 1/2 NPTF (female) x 1-11 1/2 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 1-11 1/2 NPTF (female) x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1948,7 +1953,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -1958,83 +1963,88 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Air-Way s82 only (double-pass 19 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p10 table TFA-p010-t04 "5000 FP-FP STRAIGHT" row 5000-16-08 col "L LGTH" = "1.890" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 551.2, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p10 5000 drawing: L = overall, C HEX = body hex (impact/F2a.json, certain); same-table check on today's base: 19/19 rows with an Air-Way/OMi value agree with this catalog column to rounding; CHEX@HEX: Brennan TFA catalog p10 table TFA-p010-t04 "5000 FP-FP STRAIGHT" row 5000-16-08 col "C HEX" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 551.2, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p10 5000 drawing: L = overall, C HEX = body hex (impact/F2a.json, certain); same-table check on today's base: 19/19 rows with an Air-Way/OMi value agree with this catalog column to rounding; TAPDRILL1@BORE: end library gen_straight2 FPT[16] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 1.14, FPT_P1 1.14 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; TAPDRILL2@BORE: end library gen_straight2 FPT[8] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.7, FPT_P1 0.9 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[8] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; $PRP@Threads: thread texts from the part-number dashes (NPTF lib), format of the built 5000 rows | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex from the Brennan TFA catalog p10 alone; tap drills = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>5000-16-16</t>
+          <t>5000-16-08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5000-20-16</t>
+          <t>5000-16-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1547</v>
+        <v>0.94108</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="E16" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="F16" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="G16" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="H16" t="n">
-        <v>0.965</v>
+        <v>0.945</v>
       </c>
       <c r="I16" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8096</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="M16" t="n">
-        <v>1.14</v>
+        <v>0.95</v>
       </c>
       <c r="N16" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="O16" t="n">
-        <v>0.965</v>
+        <v>0.91</v>
       </c>
       <c r="P16" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5121</v>
       </c>
       <c r="S16" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5000-20-16</t>
+          <t>5000-16-12</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 1 1/4-11 1/2 NPTF (female) x 1-11 1/2 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 1-11 1/2 NPTF (female) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2044,12 +2054,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2064,78 +2074,78 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>5000-20-16</t>
+          <t>5000-16-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5000-20-20</t>
+          <t>5000-16-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1547</v>
+        <v>0.94108</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="E17" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="F17" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="G17" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="H17" t="n">
-        <v>0.965</v>
+        <v>0.945</v>
       </c>
       <c r="I17" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8096</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="M17" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N17" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="O17" t="n">
-        <v>0.965</v>
+        <v>0.945</v>
       </c>
       <c r="P17" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8096</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>5000-20-20</t>
+          <t>5000-16-16</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 1-11 1/2 NPTF (female) x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2145,12 +2155,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2165,33 +2175,33 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>5000-20-20</t>
+          <t>5000-16-16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5000-24-24</t>
+          <t>5000-20-16</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1.93</v>
       </c>
       <c r="C18" t="n">
-        <v>1.37409</v>
+        <v>1.1547</v>
       </c>
       <c r="D18" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="F18" t="n">
         <v>1.16</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="H18" t="n">
         <v>0.965</v>
@@ -2200,19 +2210,19 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9296</v>
+        <v>0.8096</v>
       </c>
       <c r="L18" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N18" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="O18" t="n">
         <v>0.965</v>
@@ -2221,22 +2231,22 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9296</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>1.93</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5000-24-24</t>
+          <t>5000-20-16</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 1 1/4-11 1/2 NPTF (female) x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2246,12 +2256,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2266,78 +2276,78 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>5000-24-24</t>
+          <t>5000-20-16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5000-32-24</t>
+          <t>5000-20-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="C19" t="n">
-        <v>1.66277</v>
+        <v>1.1547</v>
       </c>
       <c r="D19" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="F19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="H19" t="n">
-        <v>0.98</v>
+        <v>0.965</v>
       </c>
       <c r="I19" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>0.74</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1696</v>
+        <v>0.8096</v>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
         <v>1.16</v>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="O19" t="n">
-        <v>0.98</v>
+        <v>0.965</v>
       </c>
       <c r="P19" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9296</v>
+        <v>0.8096</v>
       </c>
       <c r="S19" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>5000-32-24</t>
+          <t>5000-20-20</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Coupling, 2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>Hexagon Pipe Coupling, 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2347,12 +2357,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF (female)</t>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2365,115 +2375,423 @@
           <t>Air-Way s82 only (double-pass 19 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>TapDrill(1) 2.20 vs 32-32 2.19 for the same 2-11 1/2 thread - as-printed</t>
-        </is>
-      </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>5000-32-24</t>
+          <t>5000-20-20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5000-32-32</t>
+          <t>5000-24-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="C20" t="n">
-        <v>1.66277</v>
+        <v>1.37409</v>
       </c>
       <c r="D20" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="E20" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="F20" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="G20" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="H20" t="n">
-        <v>0.98</v>
+        <v>0.965</v>
       </c>
       <c r="I20" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.095</v>
+        <v>0.86</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1646</v>
+        <v>0.9296</v>
       </c>
       <c r="L20" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
-        <v>0.98</v>
+        <v>0.965</v>
       </c>
       <c r="P20" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="Q20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>5000-24-24</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Coupling, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Air-Way s82 only (double-pass 19 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>5000-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5000-32-24</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.1696</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>5000-32-24</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Coupling, 2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Air-Way s82 only (double-pass 19 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>TapDrill(1) 2.20 vs 32-32 2.19 for the same 2-11 1/2 thread - as-printed</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>5000-32-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5000-32-32</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J22" t="n">
         <v>1.095</v>
       </c>
-      <c r="R20" t="n">
+      <c r="K22" t="n">
         <v>1.1646</v>
       </c>
-      <c r="S20" t="n">
+      <c r="L22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.1646</v>
+      </c>
+      <c r="S22" t="n">
         <v>1.96</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>5000-32-32</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Hexagon Pipe Coupling, 2-11 1/2 NPTF (female) x 2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Air-Way s82 only (double-pass 19 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>5000-32-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5000-40-40</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.02073</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.0443</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.3645</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.4645</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.0443</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.3645</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4645</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>5000-40-40</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Coupling, 2 1/2-8 NPTF (female) x 2 1/2-8 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2 1/2-8 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2 1/2-8 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: female NPTF drill depth = MS51503 P1 max per pipe dash (2405 table); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); the two drill holes are cut to max(P1, L/2+0.005) so the coupling is through (ASSUMPTION); each helical thread is cut to min(P1, L/2) (ASSUMPTION - for -08 this equals the Brennan thread depth 0.75); hex spans the full length; -40 PIPE END (2-1/2-8 NPTF) IS BRENNAN-MEASURED, NOT ASME B1.20.1 (user 2026-10-02: Brennan-measured threads accepted for -40): male end - pitch dia at the tip E0 2.71954 = the Brennan blank cone 2.7769 (5404-40-40 / 5406-40-32 / 2501-40-40-FG STEPs) - 0.4589 P (the Brennan blank sits 0.4585-0.4595 P above ASME E0 at all 8 library sizes -04..-32, ASSUMED to hold at -40), crest E0 + 0.8P, taper 1.7899deg, thread length L2 1.1374 from D = E0 + 0.8P + (L2 - 2P)/16 with pipe OD D 2.875 (Brennan collar), end length 1.515 (measured on all four Brennan -40 male ends); female port - tap drill 2.729 and thread depth 1.0443 = the Brennan 5000-40-40 tapered port (no separate drill: the 2.729 bore runs through); 8 threads per inch = Brennan TFA catalog callout 2-1/2-8; single manufacturer, ASSUMED</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex from the Brennan TFA catalog p10 alone; -40 pipe ends not in the end library</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>5000-40-40</t>
         </is>
       </c>
     </row>
